--- a/output/pdf_financials_xlsx/SNG.xlsx
+++ b/output/pdf_financials_xlsx/SNG.xlsx
@@ -5414,13 +5414,13 @@
         <v>0.629427</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.581527</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.672193</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.788127</v>
       </c>
     </row>
     <row r="93">
@@ -6690,46 +6690,46 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-11.030213</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-10.724137</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-2.261329</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.724372</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.396525</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.492459</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-1.276413</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.323382</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.059811</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.263338</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.238056</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.19938</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.028538</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-0.185585</v>
       </c>
     </row>
     <row r="119">
@@ -8933,7 +8933,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -11007,7 +11011,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -30539,7 +30547,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -32909,7 +32921,11 @@
           <t>Deferred exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SNG.xlsx
+++ b/output/pdf_financials_xlsx/SNG.xlsx
@@ -990,43 +990,43 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.122549</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.154323</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.074129</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.050598</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.025584</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.012957</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.007125</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.007974</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.004733</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.000196</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.004991</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.009372999999999999</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.005909</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0</v>
@@ -1896,43 +1896,43 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.491853</v>
+        <v>-1.614402</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.100601</v>
+        <v>-1.254924</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.632804</v>
+        <v>-0.706933</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.562496</v>
+        <v>-0.613094</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-56.04503</v>
+        <v>-56.070614</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.001556</v>
+        <v>-1.014513</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.968007</v>
+        <v>-0.975132</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.049003</v>
+        <v>-2.056977</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.485003</v>
+        <v>-0.489736</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>4.28678</v>
+        <v>4.286584</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.191749</v>
+        <v>-1.19674</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.9873420000000001</v>
+        <v>-0.996715</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-4.176653</v>
+        <v>-4.182562</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-0.757504</v>
@@ -2002,43 +2002,43 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.491853</v>
+        <v>-1.614402</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.100601</v>
+        <v>-1.254924</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.632804</v>
+        <v>-0.706933</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.562496</v>
+        <v>-0.613094</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-56.04503</v>
+        <v>-56.070614</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.001556</v>
+        <v>-1.014513</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.968007</v>
+        <v>-0.975132</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.049003</v>
+        <v>-2.056977</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.485003</v>
+        <v>-0.489736</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>4.28678</v>
+        <v>4.286584</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.191749</v>
+        <v>-1.19674</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.9873420000000001</v>
+        <v>-0.996715</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.176653</v>
+        <v>-4.182562</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-0.757504</v>
@@ -7028,19 +7028,19 @@
         <v>0</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.018</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0135</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.018</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="P124" s="3" t="n">
         <v>0</v>
@@ -7080,19 +7080,19 @@
         <v>0</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.018</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0135</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.018</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="P125" s="3" t="n">
         <v>0</v>
@@ -13596,7 +13596,11 @@
           <t>Reclamation deposits 8</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -18149,7 +18153,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -18422,7 +18426,11 @@
           <t>Reclamation deposits 7</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -29859,7 +29867,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -31713,7 +31725,11 @@
           <t>Lease payments 7</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -32830,7 +32846,11 @@
           <t>Redemption of reclamation deposits</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -33712,7 +33732,11 @@
           <t>Reclamation deposits 8</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -33981,7 +34005,11 @@
           <t>Lease payments 7</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -34673,7 +34701,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -39716,7 +39748,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -43157,7 +43189,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -43974,7 +44006,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">

--- a/output/pdf_financials_xlsx/SNG.xlsx
+++ b/output/pdf_financials_xlsx/SNG.xlsx
@@ -6506,7 +6506,7 @@
         <v>0</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0</v>
+        <v>-0.045</v>
       </c>
       <c r="L114" s="3" t="n">
         <v>0</v>
@@ -6521,7 +6521,7 @@
         <v>0</v>
       </c>
       <c r="P114" s="3" t="n">
-        <v>0</v>
+        <v>-0.205</v>
       </c>
     </row>
     <row r="115">
@@ -6558,22 +6558,22 @@
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.01957</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.143097</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.025295</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.014835</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>1.881392</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>2.033488</v>
       </c>
     </row>
     <row r="116">
@@ -30221,7 +30221,11 @@
           <t>Purchase of marketable securities 4</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -30312,7 +30316,11 @@
           <t>Proceeds from sale of marketable securities 4</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -33914,7 +33922,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -35338,7 +35350,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -36232,7 +36248,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -45812,7 +45832,11 @@
           <t>Deferred income tax recovery 11</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
@@ -46510,7 +46534,11 @@
           <t>Deferred income tax recovery 8</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E441" t="inlineStr">
         <is>
           <t>-</t>
@@ -47032,7 +47060,11 @@
           <t>Deferred income tax recovery (expense) 8</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
           <t>-</t>
